--- a/cloudflare-deploy/public/library/student/student-kr.xlsx
+++ b/cloudflare-deploy/public/library/student/student-kr.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2245,87 @@
       <c r="E40" s="15" t="inlineStr">
         <is>
           <t>느리게로 듣고 또박또박 따라 하면 성조(4성)가 잘 잡혀요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="54" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>📔</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>AI 음성 일기</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>홈 메뉴에서 📔 AI 음성 일기 카드를 눌러요. (영어·중국어 발음 코치 카드 옆) → 🎤 녹음 탭에서 ‘녹음 시작’을 누르고 오늘 하루를 영어로 말해요. (30초 정도면 충분!) → ‘정지’를 누르면 AI가 자동으로 전사 → 첨삭 → 점수·칭찬을 만들어줘요. → 📅 캘린더 탭에서 지난 일기를 날짜별로 다시 볼 수 있어요.</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>완벽한 문장이 아니어도 괜찮아요. 매일 ‘한 문장’이라도 말하는 습관이 가장 중요해요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="54" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>🚀</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>다음은 어디로? (학습 흐름 안내)</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>웜업·학생게임·복습퀴즈·수업·단계별 발음 등을 끝까지 완료해요. → 완료 화면의 ‘🚀 다음 활동 고르기’ 버튼(또는 자동으로 뜨는 메뉴)을 확인해요. → 메뉴에서 수업 입장·AI 웜업·복습퀴즈·학생게임·녹화 다시보기·단계별 발음 등을 골라요. → 추천(⭐) 이 붙은 항목은 지금 하기 좋은 다음 활동이에요.</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>무엇을 할지 고민될 때 이 메뉴를 켜면, 오늘 공부를 매끄럽게 이어갈 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="54" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>🤖</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>A.i 상담사에게 물어보기</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>홈 화면 우하단의 A.i 상담사 아이콘을 눌러요. → 채팅창에 궁금한 점을 편하게 입력해요. (예: “복습퀴즈 어디서 해요?”) → 상담사가 답변과 함께 필요한 메뉴로 이동하도록 안내해줘요. → 🎤 마이크로 말해서 물어볼 수도 있어요.</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>“○○ 하고 싶어요”처럼 하고 싶은 걸 말하면, 그 화면으로 데려다줘요.</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F422"/>
+  <dimension ref="A1:F459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6924,12 +7005,430 @@
       <c r="E422" s="33" t="n"/>
       <c r="F422" s="33" t="n"/>
     </row>
+    <row r="424" ht="26" customHeight="1">
+      <c r="A424" s="21" t="inlineStr">
+        <is>
+          <t>38  📔 AI 음성 일기  —  오늘 하루를 영어로 말하면 AI가 첨삭해줘요</t>
+        </is>
+      </c>
+      <c r="B424" s="22" t="n"/>
+      <c r="C424" s="22" t="n"/>
+      <c r="D424" s="22" t="n"/>
+      <c r="E424" s="22" t="n"/>
+      <c r="F424" s="22" t="n"/>
+    </row>
+    <row r="425" ht="42" customHeight="1">
+      <c r="A425" s="23" t="inlineStr">
+        <is>
+          <t>📖 오늘 있었던 일을 영어로 말하면, AI가 내 발음을 글로 옮겨 적고(전사) 문장을 자연스럽게 첨삭한 뒤 점수와 칭찬을 남겨줘요. 매일 조금씩 쌓이면 나만의 영어 일기장이 완성돼요!</t>
+        </is>
+      </c>
+      <c r="B425" s="24" t="n"/>
+      <c r="C425" s="24" t="n"/>
+      <c r="D425" s="24" t="n"/>
+      <c r="E425" s="24" t="n"/>
+      <c r="F425" s="24" t="n"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B426" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" ht="30" customHeight="1">
+      <c r="A427" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B427" s="28" t="inlineStr">
+        <is>
+          <t>홈 메뉴에서 📔 AI 음성 일기 카드를 눌러요. (영어·중국어 발음 코치 카드 옆)</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="30" customHeight="1">
+      <c r="A428" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B428" s="28" t="inlineStr">
+        <is>
+          <t>🎤 녹음 탭에서 ‘녹음 시작’을 누르고 오늘 하루를 영어로 말해요. (30초 정도면 충분!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="30" customHeight="1">
+      <c r="A429" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B429" s="28" t="inlineStr">
+        <is>
+          <t>‘정지’를 누르면 AI가 자동으로 전사 → 첨삭 → 점수·칭찬을 만들어줘요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="30" customHeight="1">
+      <c r="A430" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B430" s="28" t="inlineStr">
+        <is>
+          <t>📅 캘린더 탭에서 지난 일기를 날짜별로 다시 볼 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="24" customHeight="1">
+      <c r="A431" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B431" s="30" t="inlineStr">
+        <is>
+          <t>말한 영어를 글로 바꿔주고, 어색한 문장을 자연스럽게 고쳐줘요.</t>
+        </is>
+      </c>
+      <c r="C431" s="31" t="n"/>
+      <c r="D431" s="31" t="n"/>
+      <c r="E431" s="31" t="n"/>
+      <c r="F431" s="31" t="n"/>
+    </row>
+    <row r="432" ht="24" customHeight="1">
+      <c r="A432" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B432" s="30" t="inlineStr">
+        <is>
+          <t>점수(0~100)와 한국어 격려 한마디로 매일 동기부여가 돼요.</t>
+        </is>
+      </c>
+      <c r="C432" s="31" t="n"/>
+      <c r="D432" s="31" t="n"/>
+      <c r="E432" s="31" t="n"/>
+      <c r="F432" s="31" t="n"/>
+    </row>
+    <row r="433" ht="24" customHeight="1">
+      <c r="A433" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B433" s="30" t="inlineStr">
+        <is>
+          <t>매일 하면 연속출석·배지와도 연결돼 꾸준함이 실력이 돼요.</t>
+        </is>
+      </c>
+      <c r="C433" s="31" t="n"/>
+      <c r="D433" s="31" t="n"/>
+      <c r="E433" s="31" t="n"/>
+      <c r="F433" s="31" t="n"/>
+    </row>
+    <row r="434" ht="26" customHeight="1">
+      <c r="A434" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 녹음은 로그인한 뒤 사용할 수 있어요. 조용한 곳에서 또박또박 말하면 전사가 더 정확해요.</t>
+        </is>
+      </c>
+      <c r="B434" s="35" t="n"/>
+      <c r="C434" s="35" t="n"/>
+      <c r="D434" s="35" t="n"/>
+      <c r="E434" s="35" t="n"/>
+      <c r="F434" s="35" t="n"/>
+    </row>
+    <row r="435" ht="30" customHeight="1">
+      <c r="A435" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 완벽한 문장이 아니어도 괜찮아요. 매일 ‘한 문장’이라도 말하는 습관이 가장 중요해요!</t>
+        </is>
+      </c>
+      <c r="B435" s="33" t="n"/>
+      <c r="C435" s="33" t="n"/>
+      <c r="D435" s="33" t="n"/>
+      <c r="E435" s="33" t="n"/>
+      <c r="F435" s="33" t="n"/>
+    </row>
+    <row r="437" ht="26" customHeight="1">
+      <c r="A437" s="21" t="inlineStr">
+        <is>
+          <t>39  🚀 다음은 어디로? (학습 흐름 안내)  —  한 활동이 끝나면 다음 활동을 바로 추천</t>
+        </is>
+      </c>
+      <c r="B437" s="22" t="n"/>
+      <c r="C437" s="22" t="n"/>
+      <c r="D437" s="22" t="n"/>
+      <c r="E437" s="22" t="n"/>
+      <c r="F437" s="22" t="n"/>
+    </row>
+    <row r="438" ht="42" customHeight="1">
+      <c r="A438" s="23" t="inlineStr">
+        <is>
+          <t>📖 웜업·게임·수업·복습·발음 등 한 가지 활동을 마치면, 화면에 ‘🚀 다음은 어디로 이동할까요?’ 메뉴가 떠요. 메뉴를 다시 찾아 헤맬 필요 없이, 추천 표시(⭐) 를 따라 자연스럽게 다음 활동으로 이어갈 수 있어요.</t>
+        </is>
+      </c>
+      <c r="B438" s="24" t="n"/>
+      <c r="C438" s="24" t="n"/>
+      <c r="D438" s="24" t="n"/>
+      <c r="E438" s="24" t="n"/>
+      <c r="F438" s="24" t="n"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B439" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" ht="30" customHeight="1">
+      <c r="A440" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B440" s="28" t="inlineStr">
+        <is>
+          <t>웜업·학생게임·복습퀴즈·수업·단계별 발음 등을 끝까지 완료해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441" ht="30" customHeight="1">
+      <c r="A441" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B441" s="28" t="inlineStr">
+        <is>
+          <t>완료 화면의 ‘🚀 다음 활동 고르기’ 버튼(또는 자동으로 뜨는 메뉴)을 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442" ht="30" customHeight="1">
+      <c r="A442" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B442" s="28" t="inlineStr">
+        <is>
+          <t>메뉴에서 수업 입장·AI 웜업·복습퀴즈·학생게임·녹화 다시보기·단계별 발음 등을 골라요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" ht="30" customHeight="1">
+      <c r="A443" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B443" s="28" t="inlineStr">
+        <is>
+          <t>추천(⭐) 이 붙은 항목은 지금 하기 좋은 다음 활동이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444" ht="24" customHeight="1">
+      <c r="A444" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B444" s="30" t="inlineStr">
+        <is>
+          <t>추천 흐름: 웜업 → 게임 → 수업 → 복습 → 발음 → 게임 처럼 자연스럽게 이어져요.</t>
+        </is>
+      </c>
+      <c r="C444" s="31" t="n"/>
+      <c r="D444" s="31" t="n"/>
+      <c r="E444" s="31" t="n"/>
+      <c r="F444" s="31" t="n"/>
+    </row>
+    <row r="445" ht="24" customHeight="1">
+      <c r="A445" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B445" s="30" t="inlineStr">
+        <is>
+          <t>‘녹화 다시보기’ 를 고르면 직전 수업 영상을 바로 다시 볼 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C445" s="31" t="n"/>
+      <c r="D445" s="31" t="n"/>
+      <c r="E445" s="31" t="n"/>
+      <c r="F445" s="31" t="n"/>
+    </row>
+    <row r="446" ht="24" customHeight="1">
+      <c r="A446" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B446" s="30" t="inlineStr">
+        <is>
+          <t>게임·퀴즈를 안 해도 목록 화면의 ‘🚀 다음으로 이동’ 버튼으로 메뉴를 열 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C446" s="31" t="n"/>
+      <c r="D446" s="31" t="n"/>
+      <c r="E446" s="31" t="n"/>
+      <c r="F446" s="31" t="n"/>
+    </row>
+    <row r="447" ht="30" customHeight="1">
+      <c r="A447" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 무엇을 할지 고민될 때 이 메뉴를 켜면, 오늘 공부를 매끄럽게 이어갈 수 있어요.</t>
+        </is>
+      </c>
+      <c r="B447" s="33" t="n"/>
+      <c r="C447" s="33" t="n"/>
+      <c r="D447" s="33" t="n"/>
+      <c r="E447" s="33" t="n"/>
+      <c r="F447" s="33" t="n"/>
+    </row>
+    <row r="449" ht="26" customHeight="1">
+      <c r="A449" s="21" t="inlineStr">
+        <is>
+          <t>40  🤖 A.i 상담사에게 물어보기  —  화면 우하단 상담 아바타</t>
+        </is>
+      </c>
+      <c r="B449" s="22" t="n"/>
+      <c r="C449" s="22" t="n"/>
+      <c r="D449" s="22" t="n"/>
+      <c r="E449" s="22" t="n"/>
+      <c r="F449" s="22" t="n"/>
+    </row>
+    <row r="450" ht="42" customHeight="1">
+      <c r="A450" s="23" t="inlineStr">
+        <is>
+          <t>📖 화면 오른쪽 아래에 있는 ‘A.i 상담사’ 를 누르면, 24시간 언제든 궁금한 점을 물어볼 수 있어요. 이용 방법·기능 위치·수업 안내를 알려주고, 원하면 해당 메뉴로 바로 데려다줘요.</t>
+        </is>
+      </c>
+      <c r="B450" s="24" t="n"/>
+      <c r="C450" s="24" t="n"/>
+      <c r="D450" s="24" t="n"/>
+      <c r="E450" s="24" t="n"/>
+      <c r="F450" s="24" t="n"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B451" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="452" ht="30" customHeight="1">
+      <c r="A452" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B452" s="28" t="inlineStr">
+        <is>
+          <t>홈 화면 우하단의 A.i 상담사 아이콘을 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453" ht="30" customHeight="1">
+      <c r="A453" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B453" s="28" t="inlineStr">
+        <is>
+          <t>채팅창에 궁금한 점을 편하게 입력해요. (예: “복습퀴즈 어디서 해요?”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="454" ht="30" customHeight="1">
+      <c r="A454" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B454" s="28" t="inlineStr">
+        <is>
+          <t>상담사가 답변과 함께 필요한 메뉴로 이동하도록 안내해줘요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="30" customHeight="1">
+      <c r="A455" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B455" s="28" t="inlineStr">
+        <is>
+          <t>🎤 마이크로 말해서 물어볼 수도 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="24" customHeight="1">
+      <c r="A456" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B456" s="30" t="inlineStr">
+        <is>
+          <t>학생게임·발음코치·음성일기 등 기능 위치를 바로 안내해줘요.</t>
+        </is>
+      </c>
+      <c r="C456" s="31" t="n"/>
+      <c r="D456" s="31" t="n"/>
+      <c r="E456" s="31" t="n"/>
+      <c r="F456" s="31" t="n"/>
+    </row>
+    <row r="457" ht="24" customHeight="1">
+      <c r="A457" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B457" s="30" t="inlineStr">
+        <is>
+          <t>언제든(밤·주말에도) 물어볼 수 있어 혼자서도 척척 이용할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C457" s="31" t="n"/>
+      <c r="D457" s="31" t="n"/>
+      <c r="E457" s="31" t="n"/>
+      <c r="F457" s="31" t="n"/>
+    </row>
+    <row r="458" ht="26" customHeight="1">
+      <c r="A458" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 운영·결제 등 사람이 도와야 하는 문의는 카카오톡 상담이나 고객센터로 연결돼요.</t>
+        </is>
+      </c>
+      <c r="B458" s="35" t="n"/>
+      <c r="C458" s="35" t="n"/>
+      <c r="D458" s="35" t="n"/>
+      <c r="E458" s="35" t="n"/>
+      <c r="F458" s="35" t="n"/>
+    </row>
+    <row r="459" ht="30" customHeight="1">
+      <c r="A459" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · “○○ 하고 싶어요”처럼 하고 싶은 걸 말하면, 그 화면으로 데려다줘요.</t>
+        </is>
+      </c>
+      <c r="B459" s="33" t="n"/>
+      <c r="C459" s="33" t="n"/>
+      <c r="D459" s="33" t="n"/>
+      <c r="E459" s="33" t="n"/>
+      <c r="F459" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="385">
+  <mergeCells count="419">
     <mergeCell ref="A183:F183"/>
     <mergeCell ref="B209:F209"/>
+    <mergeCell ref="B445:F445"/>
     <mergeCell ref="B301:F301"/>
     <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B432:F432"/>
     <mergeCell ref="B276:F276"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B238:F238"/>
@@ -6949,17 +7448,22 @@
     <mergeCell ref="B368:F368"/>
     <mergeCell ref="B135:F135"/>
     <mergeCell ref="B306:F306"/>
+    <mergeCell ref="B433:F433"/>
     <mergeCell ref="A252:F252"/>
     <mergeCell ref="B227:F227"/>
     <mergeCell ref="B420:F420"/>
     <mergeCell ref="B199:F199"/>
     <mergeCell ref="B370:F370"/>
+    <mergeCell ref="A438:F438"/>
     <mergeCell ref="B291:F291"/>
+    <mergeCell ref="A425:F425"/>
     <mergeCell ref="B228:F228"/>
     <mergeCell ref="A262:F262"/>
     <mergeCell ref="B88:F88"/>
     <mergeCell ref="B148:F148"/>
+    <mergeCell ref="B446:F446"/>
     <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A435:F435"/>
     <mergeCell ref="A362:F362"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B146:F146"/>
@@ -6970,12 +7474,14 @@
     <mergeCell ref="B383:F383"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A413:F413"/>
+    <mergeCell ref="B439:F439"/>
     <mergeCell ref="A375:F375"/>
     <mergeCell ref="B159:F159"/>
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="A154:F154"/>
     <mergeCell ref="A390:F390"/>
     <mergeCell ref="A129:F129"/>
+    <mergeCell ref="B441:F441"/>
     <mergeCell ref="B161:F161"/>
     <mergeCell ref="B259:F259"/>
     <mergeCell ref="B136:F136"/>
@@ -6989,6 +7495,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B91:F91"/>
     <mergeCell ref="B327:F327"/>
+    <mergeCell ref="B454:F454"/>
     <mergeCell ref="A365:F365"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B93:F93"/>
@@ -7008,9 +7515,11 @@
     <mergeCell ref="A155:F155"/>
     <mergeCell ref="B246:F246"/>
     <mergeCell ref="B40:F40"/>
+    <mergeCell ref="A437:F437"/>
     <mergeCell ref="B338:F338"/>
     <mergeCell ref="A284:F284"/>
     <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B444:F444"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B340:F340"/>
     <mergeCell ref="B79:F79"/>
@@ -7024,11 +7533,14 @@
     <mergeCell ref="A386:F386"/>
     <mergeCell ref="A373:F373"/>
     <mergeCell ref="B328:F328"/>
+    <mergeCell ref="B455:F455"/>
+    <mergeCell ref="A450:F450"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B172:F172"/>
     <mergeCell ref="B270:F270"/>
     <mergeCell ref="B392:F392"/>
     <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B457:F457"/>
     <mergeCell ref="B257:F257"/>
     <mergeCell ref="B288:F288"/>
     <mergeCell ref="B92:F92"/>
@@ -7053,6 +7565,7 @@
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="A412:F412"/>
     <mergeCell ref="A387:F387"/>
+    <mergeCell ref="A458:F458"/>
     <mergeCell ref="B359:F359"/>
     <mergeCell ref="B207:F207"/>
     <mergeCell ref="B204:F204"/>
@@ -7066,6 +7579,7 @@
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A242:F242"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B443:F443"/>
     <mergeCell ref="A244:F244"/>
     <mergeCell ref="A171:F171"/>
     <mergeCell ref="A342:F342"/>
@@ -7075,10 +7589,12 @@
     <mergeCell ref="B349:F349"/>
     <mergeCell ref="A344:F344"/>
     <mergeCell ref="A400:F400"/>
+    <mergeCell ref="B426:F426"/>
     <mergeCell ref="B226:F226"/>
     <mergeCell ref="A245:F245"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="A402:F402"/>
+    <mergeCell ref="B428:F428"/>
     <mergeCell ref="B415:F415"/>
     <mergeCell ref="A168:F168"/>
     <mergeCell ref="B63:F63"/>
@@ -7111,9 +7627,11 @@
     <mergeCell ref="B236:F236"/>
     <mergeCell ref="B307:F307"/>
     <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B429:F429"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B350:F350"/>
     <mergeCell ref="B195:F195"/>
+    <mergeCell ref="B431:F431"/>
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="B287:F287"/>
     <mergeCell ref="B358:F358"/>
@@ -7130,12 +7648,17 @@
     <mergeCell ref="B378:F378"/>
     <mergeCell ref="A422:F422"/>
     <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B442:F442"/>
     <mergeCell ref="A335:F335"/>
     <mergeCell ref="B208:F208"/>
+    <mergeCell ref="A447:F447"/>
+    <mergeCell ref="A434:F434"/>
     <mergeCell ref="B219:F219"/>
     <mergeCell ref="A213:F213"/>
     <mergeCell ref="B210:F210"/>
+    <mergeCell ref="A449:F449"/>
     <mergeCell ref="A126:F126"/>
+    <mergeCell ref="A424:F424"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B318:F318"/>
     <mergeCell ref="A190:F190"/>
@@ -7163,9 +7686,12 @@
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B145:F145"/>
     <mergeCell ref="A140:F140"/>
+    <mergeCell ref="B452:F452"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="B258:F258"/>
     <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B451:F451"/>
+    <mergeCell ref="B456:F456"/>
     <mergeCell ref="B260:F260"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="B36:F36"/>
@@ -7186,6 +7712,7 @@
     <mergeCell ref="A376:F376"/>
     <mergeCell ref="B102:F102"/>
     <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B440:F440"/>
     <mergeCell ref="B240:F240"/>
     <mergeCell ref="A234:F234"/>
     <mergeCell ref="B377:F377"/>
@@ -7199,6 +7726,7 @@
     <mergeCell ref="B89:F89"/>
     <mergeCell ref="B393:F393"/>
     <mergeCell ref="B331:F331"/>
+    <mergeCell ref="B453:F453"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B197:F197"/>
@@ -7218,6 +7746,7 @@
     <mergeCell ref="B166:F166"/>
     <mergeCell ref="B408:F408"/>
     <mergeCell ref="A332:F332"/>
+    <mergeCell ref="A459:F459"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B174:F174"/>
     <mergeCell ref="B108:F108"/>
@@ -7295,6 +7824,7 @@
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B430:F430"/>
     <mergeCell ref="B119:F119"/>
     <mergeCell ref="B290:F290"/>
     <mergeCell ref="A43:F43"/>
@@ -7302,6 +7832,7 @@
     <mergeCell ref="A170:F170"/>
     <mergeCell ref="B196:F196"/>
     <mergeCell ref="B367:F367"/>
+    <mergeCell ref="B427:F427"/>
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="B348:F348"/>
     <mergeCell ref="B419:F419"/>

--- a/cloudflare-deploy/public/library/student/student-kr.xlsx
+++ b/cloudflare-deploy/public/library/student/student-kr.xlsx
@@ -1108,7 +1108,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>🌐 test.mangoi.co.kr    📞 1588-0000    ✉ support@mangoi.co.kr</t>
+          <t>🌐 www.mangoi.co.kr    📞 1644-0561    ✉ support@mangoi.co.kr</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>브라우저에서 test.mangoi.co.kr 에 접속하고 로그인해요. (소셜 로그인도 가능) → 오른쪽 위에서 내 이름·포인트(P) 로 로그인 상태를 확인해요. → 왼쪽 ‘열림’ 탭을 누르면 메뉴 사이드바가 펼쳐져요. → 오른쪽 아래 A.i 상담사에게 궁금한 걸 물어볼 수 있어요. → EN 버튼으로 화면 글자를 영어로 바꿀 수 있어요.</t>
+          <t>브라우저에서 www.mangoi.co.kr 에 접속하고 로그인해요. (소셜 로그인도 가능) → 오른쪽 위에서 내 이름·포인트(P) 로 로그인 상태를 확인해요. → 왼쪽 ‘열림’ 탭을 누르면 메뉴 사이드바가 펼쳐져요. → 오른쪽 아래 A.i 상담사에게 궁금한 걸 물어볼 수 있어요. → EN 버튼으로 화면 글자를 영어로 바꿀 수 있어요.</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="B6" s="28" t="inlineStr">
         <is>
-          <t>브라우저에서 test.mangoi.co.kr 에 접속하고 로그인해요. (소셜 로그인도 가능)</t>
+          <t>브라우저에서 www.mangoi.co.kr 에 접속하고 로그인해요. (소셜 로그인도 가능)</t>
         </is>
       </c>
     </row>

--- a/cloudflare-deploy/public/library/student/student-kr.xlsx
+++ b/cloudflare-deploy/public/library/student/student-kr.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2326,6 +2326,87 @@
       <c r="E43" s="20" t="inlineStr">
         <is>
           <t>“○○ 하고 싶어요”처럼 하고 싶은 걸 말하면, 그 화면으로 데려다줘요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="54" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>🎛️</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>수업 화면 새 편의 기능</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>내 얼굴 타일의 🙈 버튼을 누르면 얼굴이 잠시 숨겨져요. 🙂 칩을 누르면 다시 나와요. → 수업에 들어가면 선생님 얼굴이 맨 위에 크게 자동 배치돼요. 찾을 필요 없어요. → 휴대폰(세로) 은 위엔 얼굴, 아래엔 교재가 반반 나오는 화면이 기본이에요. → 휴대폰 하단 도구모음은 ⋯ 버튼을 눌렀을 때만 펼쳐져 화면이 넓게 쓰여요.</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>화면이 좁게 느껴지면 ⋯ 버튼으로 도구모음을 접어보세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="54" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>💬</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>1:1 개별 채팅 &amp; 파일 보내기</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>하단 독의 💬 채팅을 열어요. → 받는 사람을 전체에서 선생님 이름으로 바꾸면 1:1 귓속말이 돼요. → 📎 파일 버튼으로 PDF·사진·문서를 올리면 상대 화면에 다운로드 카드가 생겨요. → 받은 파일은 카드의 ⬇ 저장을 눌러 내려받아요.</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>수업 중 궁금한 걸 다른 친구 방해 없이 조용히 물어볼 때 딱 좋아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="54" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>🌗</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>홈 화면 밝게 · 어둡게</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>홈 화면 상단의 🌗 테마 칩을 찾아요. → 밝게 · 자동 · 어둡게 중 원하는 것을 눌러요. → 자동으로 두면 아침엔 화사하게, 밤엔 눈이 편한 어두운 화면으로 스스로 바뀌어요.</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>자기 전 복습할 땐 어둡게, 아침 웜업 땐 밝게 — 기분까지 바뀌어요!</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F459"/>
+  <dimension ref="A1:F493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7421,8 +7502,382 @@
       <c r="E459" s="33" t="n"/>
       <c r="F459" s="33" t="n"/>
     </row>
+    <row r="461" ht="26" customHeight="1">
+      <c r="A461" s="21" t="inlineStr">
+        <is>
+          <t>41  🎛️ 수업 화면 새 편의 기능  —  얼굴 숨김 · 교사 얼굴 먼저 · 모바일 도구모음</t>
+        </is>
+      </c>
+      <c r="B461" s="22" t="n"/>
+      <c r="C461" s="22" t="n"/>
+      <c r="D461" s="22" t="n"/>
+      <c r="E461" s="22" t="n"/>
+      <c r="F461" s="22" t="n"/>
+    </row>
+    <row r="462" ht="42" customHeight="1">
+      <c r="A462" s="23" t="inlineStr">
+        <is>
+          <t>📖 수업 화면이 더 편해졌어요. 내 얼굴을 잠시 숨길 수 있는 🙈 버튼, 입장하면 선생님 얼굴이 맨 위에 크게 보이는 배치, 휴대폰에서는 ⋯ 버튼으로 필요할 때만 여는 도구모음까지 — 수업에만 집중할 수 있게 정돈했어요.</t>
+        </is>
+      </c>
+      <c r="B462" s="24" t="n"/>
+      <c r="C462" s="24" t="n"/>
+      <c r="D462" s="24" t="n"/>
+      <c r="E462" s="24" t="n"/>
+      <c r="F462" s="24" t="n"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B463" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="30" customHeight="1">
+      <c r="A464" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B464" s="28" t="inlineStr">
+        <is>
+          <t>내 얼굴 타일의 🙈 버튼을 누르면 얼굴이 잠시 숨겨져요. 🙂 칩을 누르면 다시 나와요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" ht="30" customHeight="1">
+      <c r="A465" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B465" s="28" t="inlineStr">
+        <is>
+          <t>수업에 들어가면 선생님 얼굴이 맨 위에 크게 자동 배치돼요. 찾을 필요 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466" ht="30" customHeight="1">
+      <c r="A466" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B466" s="28" t="inlineStr">
+        <is>
+          <t>휴대폰(세로) 은 위엔 얼굴, 아래엔 교재가 반반 나오는 화면이 기본이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" ht="30" customHeight="1">
+      <c r="A467" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B467" s="28" t="inlineStr">
+        <is>
+          <t>휴대폰 하단 도구모음은 ⋯ 버튼을 눌렀을 때만 펼쳐져 화면이 넓게 쓰여요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468" ht="24" customHeight="1">
+      <c r="A468" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B468" s="30" t="inlineStr">
+        <is>
+          <t>카메라를 끄는 게 아니라 화면에서만 잠시 숨기는 거라 수업은 그대로 이어져요.</t>
+        </is>
+      </c>
+      <c r="C468" s="31" t="n"/>
+      <c r="D468" s="31" t="n"/>
+      <c r="E468" s="31" t="n"/>
+      <c r="F468" s="31" t="n"/>
+    </row>
+    <row r="469" ht="24" customHeight="1">
+      <c r="A469" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B469" s="30" t="inlineStr">
+        <is>
+          <t>가로로 돌리면 왼쪽 얼굴 · 오른쪽 교재로 자동 정돈돼요.</t>
+        </is>
+      </c>
+      <c r="C469" s="31" t="n"/>
+      <c r="D469" s="31" t="n"/>
+      <c r="E469" s="31" t="n"/>
+      <c r="F469" s="31" t="n"/>
+    </row>
+    <row r="470" ht="26" customHeight="1">
+      <c r="A470" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 얼굴 숨김은 부끄러울 때 잠깐만! 선생님과 눈을 맞추며 수업하면 훨씬 재미있어요.</t>
+        </is>
+      </c>
+      <c r="B470" s="35" t="n"/>
+      <c r="C470" s="35" t="n"/>
+      <c r="D470" s="35" t="n"/>
+      <c r="E470" s="35" t="n"/>
+      <c r="F470" s="35" t="n"/>
+    </row>
+    <row r="471" ht="30" customHeight="1">
+      <c r="A471" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 화면이 좁게 느껴지면 ⋯ 버튼으로 도구모음을 접어보세요.</t>
+        </is>
+      </c>
+      <c r="B471" s="33" t="n"/>
+      <c r="C471" s="33" t="n"/>
+      <c r="D471" s="33" t="n"/>
+      <c r="E471" s="33" t="n"/>
+      <c r="F471" s="33" t="n"/>
+    </row>
+    <row r="473" ht="26" customHeight="1">
+      <c r="A473" s="21" t="inlineStr">
+        <is>
+          <t>42  💬 1:1 개별 채팅 &amp; 파일 보내기  —  선생님에게만 보이는 귓속말 + 모든 파일 공유</t>
+        </is>
+      </c>
+      <c r="B473" s="22" t="n"/>
+      <c r="C473" s="22" t="n"/>
+      <c r="D473" s="22" t="n"/>
+      <c r="E473" s="22" t="n"/>
+      <c r="F473" s="22" t="n"/>
+    </row>
+    <row r="474" ht="42" customHeight="1">
+      <c r="A474" s="23" t="inlineStr">
+        <is>
+          <t>📖 수업 채팅에 1:1 개별 채팅(DM) 이 생겼어요. 특정 선생님에게만 보이는 메시지를 보낼 수 있고, PDF·이미지·문서 등 어떤 파일이든 채팅으로 공유하면 상대방 화면에 다운로드 카드로 떠요.</t>
+        </is>
+      </c>
+      <c r="B474" s="24" t="n"/>
+      <c r="C474" s="24" t="n"/>
+      <c r="D474" s="24" t="n"/>
+      <c r="E474" s="24" t="n"/>
+      <c r="F474" s="24" t="n"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B475" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="476" ht="30" customHeight="1">
+      <c r="A476" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B476" s="28" t="inlineStr">
+        <is>
+          <t>하단 독의 💬 채팅을 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477" ht="30" customHeight="1">
+      <c r="A477" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B477" s="28" t="inlineStr">
+        <is>
+          <t>받는 사람을 전체에서 선생님 이름으로 바꾸면 1:1 귓속말이 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" ht="30" customHeight="1">
+      <c r="A478" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B478" s="28" t="inlineStr">
+        <is>
+          <t>📎 파일 버튼으로 PDF·사진·문서를 올리면 상대 화면에 다운로드 카드가 생겨요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479" ht="30" customHeight="1">
+      <c r="A479" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B479" s="28" t="inlineStr">
+        <is>
+          <t>받은 파일은 카드의 ⬇ 저장을 눌러 내려받아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="24" customHeight="1">
+      <c r="A480" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B480" s="30" t="inlineStr">
+        <is>
+          <t>개별 채팅은 당사자끼리만 보여요.</t>
+        </is>
+      </c>
+      <c r="C480" s="31" t="n"/>
+      <c r="D480" s="31" t="n"/>
+      <c r="E480" s="31" t="n"/>
+      <c r="F480" s="31" t="n"/>
+    </row>
+    <row r="481" ht="24" customHeight="1">
+      <c r="A481" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B481" s="30" t="inlineStr">
+        <is>
+          <t>숙제 파일·오답 정리 등 수업 자료 주고받기가 한 번에 끝나요.</t>
+        </is>
+      </c>
+      <c r="C481" s="31" t="n"/>
+      <c r="D481" s="31" t="n"/>
+      <c r="E481" s="31" t="n"/>
+      <c r="F481" s="31" t="n"/>
+    </row>
+    <row r="482" ht="26" customHeight="1">
+      <c r="A482" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 개별 채팅 내용은 서버에 저장되지 않아 수업이 끝나면 사라져요. 중요한 내용은 파일로 보관하세요.</t>
+        </is>
+      </c>
+      <c r="B482" s="35" t="n"/>
+      <c r="C482" s="35" t="n"/>
+      <c r="D482" s="35" t="n"/>
+      <c r="E482" s="35" t="n"/>
+      <c r="F482" s="35" t="n"/>
+    </row>
+    <row r="483" ht="30" customHeight="1">
+      <c r="A483" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 수업 중 궁금한 걸 다른 친구 방해 없이 조용히 물어볼 때 딱 좋아요.</t>
+        </is>
+      </c>
+      <c r="B483" s="33" t="n"/>
+      <c r="C483" s="33" t="n"/>
+      <c r="D483" s="33" t="n"/>
+      <c r="E483" s="33" t="n"/>
+      <c r="F483" s="33" t="n"/>
+    </row>
+    <row r="485" ht="26" customHeight="1">
+      <c r="A485" s="21" t="inlineStr">
+        <is>
+          <t>43  🌗 홈 화면 밝게 · 어둡게  —  시간대에 맞춰 자동으로, 원하면 내 맘대로</t>
+        </is>
+      </c>
+      <c r="B485" s="22" t="n"/>
+      <c r="C485" s="22" t="n"/>
+      <c r="D485" s="22" t="n"/>
+      <c r="E485" s="22" t="n"/>
+      <c r="F485" s="22" t="n"/>
+    </row>
+    <row r="486" ht="42" customHeight="1">
+      <c r="A486" s="23" t="inlineStr">
+        <is>
+          <t>📖 홈 화면이 시간대에 따라 자동으로 낮엔 밝게, 밤엔 어둡게 바뀌어요. 물론 밝게/자동/어둡게 3단 버튼으로 언제든 원하는 분위기를 직접 고를 수도 있어요.</t>
+        </is>
+      </c>
+      <c r="B486" s="24" t="n"/>
+      <c r="C486" s="24" t="n"/>
+      <c r="D486" s="24" t="n"/>
+      <c r="E486" s="24" t="n"/>
+      <c r="F486" s="24" t="n"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B487" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" ht="30" customHeight="1">
+      <c r="A488" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B488" s="28" t="inlineStr">
+        <is>
+          <t>홈 화면 상단의 🌗 테마 칩을 찾아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489" ht="30" customHeight="1">
+      <c r="A489" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B489" s="28" t="inlineStr">
+        <is>
+          <t>밝게 · 자동 · 어둡게 중 원하는 것을 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490" ht="30" customHeight="1">
+      <c r="A490" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B490" s="28" t="inlineStr">
+        <is>
+          <t>자동으로 두면 아침엔 화사하게, 밤엔 눈이 편한 어두운 화면으로 스스로 바뀌어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" ht="24" customHeight="1">
+      <c r="A491" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B491" s="30" t="inlineStr">
+        <is>
+          <t>밤 늦게 공부할 때 눈부심이 줄어 편해요.</t>
+        </is>
+      </c>
+      <c r="C491" s="31" t="n"/>
+      <c r="D491" s="31" t="n"/>
+      <c r="E491" s="31" t="n"/>
+      <c r="F491" s="31" t="n"/>
+    </row>
+    <row r="492" ht="24" customHeight="1">
+      <c r="A492" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B492" s="30" t="inlineStr">
+        <is>
+          <t>선택한 테마는 다음 접속 때도 그대로 기억돼요.</t>
+        </is>
+      </c>
+      <c r="C492" s="31" t="n"/>
+      <c r="D492" s="31" t="n"/>
+      <c r="E492" s="31" t="n"/>
+      <c r="F492" s="31" t="n"/>
+    </row>
+    <row r="493" ht="30" customHeight="1">
+      <c r="A493" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 자기 전 복습할 땐 어둡게, 아침 웜업 땐 밝게 — 기분까지 바뀌어요!</t>
+        </is>
+      </c>
+      <c r="B493" s="33" t="n"/>
+      <c r="C493" s="33" t="n"/>
+      <c r="D493" s="33" t="n"/>
+      <c r="E493" s="33" t="n"/>
+      <c r="F493" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="419">
+  <mergeCells count="450">
     <mergeCell ref="A183:F183"/>
     <mergeCell ref="B209:F209"/>
     <mergeCell ref="B445:F445"/>
@@ -7445,6 +7900,8 @@
     <mergeCell ref="A315:F315"/>
     <mergeCell ref="B356:F356"/>
     <mergeCell ref="B160:F160"/>
+    <mergeCell ref="A486:F486"/>
+    <mergeCell ref="B489:F489"/>
     <mergeCell ref="B368:F368"/>
     <mergeCell ref="B135:F135"/>
     <mergeCell ref="B306:F306"/>
@@ -7471,6 +7928,7 @@
     <mergeCell ref="B217:F217"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="B319:F319"/>
+    <mergeCell ref="B490:F490"/>
     <mergeCell ref="B383:F383"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A413:F413"/>
@@ -7513,10 +7971,12 @@
     <mergeCell ref="A389:F389"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="A155:F155"/>
+    <mergeCell ref="B467:F467"/>
     <mergeCell ref="B246:F246"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="A437:F437"/>
     <mergeCell ref="B338:F338"/>
+    <mergeCell ref="B469:F469"/>
     <mergeCell ref="A284:F284"/>
     <mergeCell ref="B177:F177"/>
     <mergeCell ref="B444:F444"/>
@@ -7531,10 +7991,12 @@
     <mergeCell ref="B366:F366"/>
     <mergeCell ref="B381:F381"/>
     <mergeCell ref="A386:F386"/>
+    <mergeCell ref="B480:F480"/>
     <mergeCell ref="A373:F373"/>
     <mergeCell ref="B328:F328"/>
     <mergeCell ref="B455:F455"/>
     <mergeCell ref="A450:F450"/>
+    <mergeCell ref="B491:F491"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B172:F172"/>
     <mergeCell ref="B270:F270"/>
@@ -7545,6 +8007,7 @@
     <mergeCell ref="B288:F288"/>
     <mergeCell ref="B92:F92"/>
     <mergeCell ref="B394:F394"/>
+    <mergeCell ref="A462:F462"/>
     <mergeCell ref="A399:F399"/>
     <mergeCell ref="A355:F355"/>
     <mergeCell ref="A305:F305"/>
@@ -7553,10 +8016,12 @@
     <mergeCell ref="B125:F125"/>
     <mergeCell ref="B185:F185"/>
     <mergeCell ref="A223:F223"/>
+    <mergeCell ref="B475:F475"/>
     <mergeCell ref="A294:F294"/>
     <mergeCell ref="B176:F176"/>
     <mergeCell ref="B347:F347"/>
     <mergeCell ref="B341:F341"/>
+    <mergeCell ref="B468:F468"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="A254:F254"/>
     <mergeCell ref="B405:F405"/>
@@ -7564,6 +8029,7 @@
     <mergeCell ref="A314:F314"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="A412:F412"/>
+    <mergeCell ref="B463:F463"/>
     <mergeCell ref="A387:F387"/>
     <mergeCell ref="A458:F458"/>
     <mergeCell ref="B359:F359"/>
@@ -7587,11 +8053,14 @@
     <mergeCell ref="A115:F115"/>
     <mergeCell ref="B178:F178"/>
     <mergeCell ref="B349:F349"/>
+    <mergeCell ref="B476:F476"/>
     <mergeCell ref="A344:F344"/>
     <mergeCell ref="A400:F400"/>
+    <mergeCell ref="A471:F471"/>
     <mergeCell ref="B426:F426"/>
     <mergeCell ref="B226:F226"/>
     <mergeCell ref="A245:F245"/>
+    <mergeCell ref="B478:F478"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="A402:F402"/>
     <mergeCell ref="B428:F428"/>
@@ -7602,6 +8071,7 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B110:F110"/>
     <mergeCell ref="B286:F286"/>
+    <mergeCell ref="B479:F479"/>
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="A255:F255"/>
     <mergeCell ref="A364:F364"/>
@@ -7618,17 +8088,21 @@
     <mergeCell ref="B205:F205"/>
     <mergeCell ref="B339:F339"/>
     <mergeCell ref="A352:F352"/>
+    <mergeCell ref="A485:F485"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A410:F410"/>
     <mergeCell ref="B194:F194"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="A118:F118"/>
+    <mergeCell ref="B492:F492"/>
+    <mergeCell ref="A474:F474"/>
     <mergeCell ref="B131:F131"/>
     <mergeCell ref="B236:F236"/>
     <mergeCell ref="B307:F307"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B429:F429"/>
     <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B465:F465"/>
     <mergeCell ref="B350:F350"/>
     <mergeCell ref="B195:F195"/>
     <mergeCell ref="B431:F431"/>
@@ -7661,6 +8135,7 @@
     <mergeCell ref="A424:F424"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B318:F318"/>
+    <mergeCell ref="A482:F482"/>
     <mergeCell ref="A190:F190"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B308:F308"/>
@@ -7674,6 +8149,7 @@
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B361:F361"/>
+    <mergeCell ref="A493:F493"/>
     <mergeCell ref="B150:F150"/>
     <mergeCell ref="B321:F321"/>
     <mergeCell ref="B215:F215"/>
@@ -7691,6 +8167,7 @@
     <mergeCell ref="B258:F258"/>
     <mergeCell ref="B147:F147"/>
     <mergeCell ref="B451:F451"/>
+    <mergeCell ref="B481:F481"/>
     <mergeCell ref="B456:F456"/>
     <mergeCell ref="B260:F260"/>
     <mergeCell ref="A94:F94"/>
@@ -7745,6 +8222,7 @@
     <mergeCell ref="B250:F250"/>
     <mergeCell ref="B166:F166"/>
     <mergeCell ref="B408:F408"/>
+    <mergeCell ref="B464:F464"/>
     <mergeCell ref="A332:F332"/>
     <mergeCell ref="A459:F459"/>
     <mergeCell ref="B37:F37"/>
@@ -7752,9 +8230,12 @@
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="B230:F230"/>
     <mergeCell ref="B279:F279"/>
+    <mergeCell ref="B466:F466"/>
+    <mergeCell ref="B477:F477"/>
     <mergeCell ref="B281:F281"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B256:F256"/>
+    <mergeCell ref="A473:F473"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B134:F134"/>
@@ -7779,10 +8260,12 @@
     <mergeCell ref="A182:F182"/>
     <mergeCell ref="A304:F304"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="A461:F461"/>
     <mergeCell ref="B251:F251"/>
     <mergeCell ref="B189:F189"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B216:F216"/>
+    <mergeCell ref="B487:F487"/>
     <mergeCell ref="B414:F414"/>
     <mergeCell ref="B188:F188"/>
     <mergeCell ref="B109:F109"/>
@@ -7793,6 +8276,7 @@
     <mergeCell ref="B416:F416"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B488:F488"/>
     <mergeCell ref="A179:F179"/>
     <mergeCell ref="B409:F409"/>
     <mergeCell ref="A322:F322"/>
@@ -7820,8 +8304,10 @@
     <mergeCell ref="B130:F130"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A312:F312"/>
+    <mergeCell ref="A483:F483"/>
     <mergeCell ref="A106:F106"/>
     <mergeCell ref="B67:F67"/>
+    <mergeCell ref="A470:F470"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B430:F430"/>

--- a/cloudflare-deploy/public/library/student/student-kr.xlsx
+++ b/cloudflare-deploy/public/library/student/student-kr.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2407,6 +2407,195 @@
       <c r="E46" s="15" t="inlineStr">
         <is>
           <t>자기 전 복습할 땐 어둡게, 아침 웜업 땐 밝게 — 기분까지 바뀌어요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="54" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>🧠</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>판단력 훈련 (상황에 맞는 말 고르기)</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>학생 홈의 AI 학습 도구에서 🧠 판단력 훈련을 열어요. → 이런 상황이에요 를 읽고 A~D 중 하나를 골라요. → 왜 그 표현을 골랐어요? 칸에 이유를 적어요. 한국어로 써도 괜찮아요. → 제출하기를 누르면 AI가 점수와 함께 왜 그게 더 좋은 표현인지 설명해 줘요. → 오른쪽 위 🏅 내 성장에서 판단력 지수와 5가지 축을 확인해요.</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>틀려도 괜찮아요. 왜 그렇게 생각했는지를 쓰는 것이 이 훈련의 핵심이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="54" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>🍕</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>문법 피자 마스터 (어순 조립)</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>학습 게임 허브에서 🍕 문법 피자 마스터를 열어요. → 듣고 시작하기를 눌러 문장을 먼저 들어요. → 아래 재료를 문장 순서대로 피자 위에 올려요. → 막히면 오른쪽 위 💡 힌트! 를 눌러요. → 레벨 1 → 2 → 3으로 문장이 점점 길어져요.</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>소리 내어 따라 읽으면서 올리면 어순이 훨씬 빨리 몸에 붙어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="54" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>🧱</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>단어 테트리스</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>학습 게임 허브에서 🧱 단어 테트리스를 열어요. → US 영어 모드 / CN 중국어 모드 중 하나를 골라요. → ◀ ▶ 이동 · 회전 · ▼ 빨리 · ↓ 한번에 떨어뜨리기로 조각을 놓아요. → 조각을 놓을 때마다 발음이 들려요 — 듣고 따라 하세요.</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>긴 단어를 먼저 아래쪽에 깔아두면 줄을 훨씬 쉽게 채울 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="54" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>셔먼 탱크대전 · 랭귀지 에이스</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>학습 게임 허브에서 🛡️ 셔먼 탱크대전 또는 ✈️ 랭귀지 에이스를 열어요. → 탱크대전은 English / 中文과 전장(초원·사막·설원), 난이도 1~7을 골라요. → 왼쪽 버튼을 누른 채 끌면 이동, 짧게 탭하면 그 방향으로 발사예요. → 위 문장의 금색 단어를 실은 전차를 순서대로 격파해요. → 젤리 연료통을 먹으면 시간이 늘어나요.</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>게임은 수업 뒤 복습용으로 쓸 때 효과가 가장 좋아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="54" customHeight="1">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>🔐</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>얼굴 · 지문으로 로그인 (패스키)</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>앱을 최신 버전(v1.9 이상) 으로 올려요. → 평소처럼 아이디·비밀번호로 한 번 로그인해요. → 안내가 뜨면 패스키 등록을 눌러 얼굴·지문을 등록해요. → 다음부터는 로그인 화면에서 얼굴·지문으로 바로 들어가요.</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>어린 학생일수록 비밀번호를 자주 잊어버려요. 패스키를 등록해 두면 문의가 크게 줄어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="54" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🎤</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>말하기가 잘 안 끊겨요 · AI 친구도 똑똑해졌어요</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>말하기 코치·AI 웜업·AI 친구에서 🎤 버튼을 눌러 말해요. → 생각하느라 잠깐 멈춰도 괜찮아요 — 끝났다고 판단할 때까지 기다려요. → AI 친구에게 “천천히 말해 줘” 라고 하면 속도를 낮춰서 말해 줘요. → 목소리는 남자 · 여자 · 번갈아 중에서 고를 수 있어요.</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>이어폰 마이크를 쓰면 인식률이 눈에 띄게 올라가요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="54" customHeight="1">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>💳</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>수강신청 · 결제 한 번에</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>수강신청 화면을 열어요. → ① 강사 선택 — 원하는 선생님을 골라요. → ② 수업 옵션 — 주 횟수(주1~5회) · 기간(1·3·6·12개월) · 수업 길이(20분/40분)를 골라요. → ③ 요일·시간 — 요일을 주 횟수만큼 고르고 시작 시각·시작일을 정해요. → ✅ 예약 가능이 뜨면 아래 결제하기를 눌러요. → 결제가 끝나면 전체 회차가 한꺼번에 생성돼요. 마이페이지에서 확인하세요.</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>학교 일정이 있는 요일은 피해서 고르세요. 나중에 바꾸는 것보다 처음에 잘 고르는 게 편해요.</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F493"/>
+  <dimension ref="A1:F588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7876,25 +8065,1112 @@
       <c r="E493" s="33" t="n"/>
       <c r="F493" s="33" t="n"/>
     </row>
+    <row r="495" ht="26" customHeight="1">
+      <c r="A495" s="21" t="inlineStr">
+        <is>
+          <t>44  🧠 판단력 훈련 (상황에 맞는 말 고르기)  —  정답 외우기 말고 · 지금 어떤 말이 맞을까?</t>
+        </is>
+      </c>
+      <c r="B495" s="22" t="n"/>
+      <c r="C495" s="22" t="n"/>
+      <c r="D495" s="22" t="n"/>
+      <c r="E495" s="22" t="n"/>
+      <c r="F495" s="22" t="n"/>
+    </row>
+    <row r="496" ht="42" customHeight="1">
+      <c r="A496" s="23" t="inlineStr">
+        <is>
+          <t>📖 AI가 실제로 있을 법한 상황을 하나 만들어 주면, 보기 중에서 그 상황에 가장 잘 맞는 표현을 고르고 왜 그렇게 골랐는지 한 줄 적는 훈련이에요. 친구에게는 “Give me that!”이 자연스럽지만 선생님께는 “Could I have that, please?”가 맞는 것처럼 — 영어는 많이 아는 힘보다 지금 어떤 말이 맞는지 판단하는 힘이 진짜 실력이거든요.</t>
+        </is>
+      </c>
+      <c r="B496" s="24" t="n"/>
+      <c r="C496" s="24" t="n"/>
+      <c r="D496" s="24" t="n"/>
+      <c r="E496" s="24" t="n"/>
+      <c r="F496" s="24" t="n"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B497" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="498" ht="30" customHeight="1">
+      <c r="A498" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B498" s="28" t="inlineStr">
+        <is>
+          <t>학생 홈의 AI 학습 도구에서 🧠 판단력 훈련을 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499" ht="30" customHeight="1">
+      <c r="A499" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B499" s="28" t="inlineStr">
+        <is>
+          <t>이런 상황이에요 를 읽고 A~D 중 하나를 골라요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500" ht="30" customHeight="1">
+      <c r="A500" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B500" s="28" t="inlineStr">
+        <is>
+          <t>왜 그 표현을 골랐어요? 칸에 이유를 적어요. 한국어로 써도 괜찮아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501" ht="30" customHeight="1">
+      <c r="A501" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B501" s="28" t="inlineStr">
+        <is>
+          <t>제출하기를 누르면 AI가 점수와 함께 왜 그게 더 좋은 표현인지 설명해 줘요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502" ht="30" customHeight="1">
+      <c r="A502" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B502" s="28" t="inlineStr">
+        <is>
+          <t>오른쪽 위 🏅 내 성장에서 판단력 지수와 5가지 축을 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503" ht="24" customHeight="1">
+      <c r="A503" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B503" s="30" t="inlineStr">
+        <is>
+          <t>보기마다 부분 점수가 있어요. 완전 오답만 아니면 점수를 받아요.</t>
+        </is>
+      </c>
+      <c r="C503" s="31" t="n"/>
+      <c r="D503" s="31" t="n"/>
+      <c r="E503" s="31" t="n"/>
+      <c r="F503" s="31" t="n"/>
+    </row>
+    <row r="504" ht="24" customHeight="1">
+      <c r="A504" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B504" s="30" t="inlineStr">
+        <is>
+          <t>이유를 잘 설명할수록 점수가 올라가요 — 생각을 말로 푸는 연습이에요.</t>
+        </is>
+      </c>
+      <c r="C504" s="31" t="n"/>
+      <c r="D504" s="31" t="n"/>
+      <c r="E504" s="31" t="n"/>
+      <c r="F504" s="31" t="n"/>
+    </row>
+    <row r="505" ht="24" customHeight="1">
+      <c r="A505" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B505" s="30" t="inlineStr">
+        <is>
+          <t>교재와 연계돼요(예: Side by Side 2). 배운 범위 안에서 문제가 나와요.</t>
+        </is>
+      </c>
+      <c r="C505" s="31" t="n"/>
+      <c r="D505" s="31" t="n"/>
+      <c r="E505" s="31" t="n"/>
+      <c r="F505" s="31" t="n"/>
+    </row>
+    <row r="506" ht="24" customHeight="1">
+      <c r="A506" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B506" s="30" t="inlineStr">
+        <is>
+          <t>매번 다른 주제·다른 각도로 나와서 같은 문제가 반복되지 않아요.</t>
+        </is>
+      </c>
+      <c r="C506" s="31" t="n"/>
+      <c r="D506" s="31" t="n"/>
+      <c r="E506" s="31" t="n"/>
+      <c r="F506" s="31" t="n"/>
+    </row>
+    <row r="507" ht="26" customHeight="1">
+      <c r="A507" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · AI가 문제를 만드는 데 몇 초 걸릴 수 있어요. 다음 문제는 푸는 동안 미리 준비되니 대부분 바로 뜹니다.</t>
+        </is>
+      </c>
+      <c r="B507" s="35" t="n"/>
+      <c r="C507" s="35" t="n"/>
+      <c r="D507" s="35" t="n"/>
+      <c r="E507" s="35" t="n"/>
+      <c r="F507" s="35" t="n"/>
+    </row>
+    <row r="508" ht="30" customHeight="1">
+      <c r="A508" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 틀려도 괜찮아요. 왜 그렇게 생각했는지를 쓰는 것이 이 훈련의 핵심이에요.</t>
+        </is>
+      </c>
+      <c r="B508" s="33" t="n"/>
+      <c r="C508" s="33" t="n"/>
+      <c r="D508" s="33" t="n"/>
+      <c r="E508" s="33" t="n"/>
+      <c r="F508" s="33" t="n"/>
+    </row>
+    <row r="510" ht="26" customHeight="1">
+      <c r="A510" s="21" t="inlineStr">
+        <is>
+          <t>45  🍕 문법 피자 마스터 (어순 조립)  —  재료를 순서대로 올려 문장 완성</t>
+        </is>
+      </c>
+      <c r="B510" s="22" t="n"/>
+      <c r="C510" s="22" t="n"/>
+      <c r="D510" s="22" t="n"/>
+      <c r="E510" s="22" t="n"/>
+      <c r="F510" s="22" t="n"/>
+    </row>
+    <row r="511" ht="42" customHeight="1">
+      <c r="A511" s="23" t="inlineStr">
+        <is>
+          <t>📖 단어가 피자 재료로 나와요. 문장을 먼저 듣고, 문장 순서대로 재료를 피자 위에 올리면 완성! 주어·동사·목적어가 색으로 구분돼 있어서 영어 어순이 눈으로 익혀지는 게임이에요.</t>
+        </is>
+      </c>
+      <c r="B511" s="24" t="n"/>
+      <c r="C511" s="24" t="n"/>
+      <c r="D511" s="24" t="n"/>
+      <c r="E511" s="24" t="n"/>
+      <c r="F511" s="24" t="n"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B512" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="513" ht="30" customHeight="1">
+      <c r="A513" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B513" s="28" t="inlineStr">
+        <is>
+          <t>학습 게임 허브에서 🍕 문법 피자 마스터를 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514" ht="30" customHeight="1">
+      <c r="A514" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B514" s="28" t="inlineStr">
+        <is>
+          <t>듣고 시작하기를 눌러 문장을 먼저 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515" ht="30" customHeight="1">
+      <c r="A515" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B515" s="28" t="inlineStr">
+        <is>
+          <t>아래 재료를 문장 순서대로 피자 위에 올려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516" ht="30" customHeight="1">
+      <c r="A516" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B516" s="28" t="inlineStr">
+        <is>
+          <t>막히면 오른쪽 위 💡 힌트! 를 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517" ht="30" customHeight="1">
+      <c r="A517" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B517" s="28" t="inlineStr">
+        <is>
+          <t>레벨 1 → 2 → 3으로 문장이 점점 길어져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518" ht="24" customHeight="1">
+      <c r="A518" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B518" s="30" t="inlineStr">
+        <is>
+          <t>재료 아래에 주어·동사·목적어 라벨이 붙어 있어 어순이 자연스럽게 익혀져요.</t>
+        </is>
+      </c>
+      <c r="C518" s="31" t="n"/>
+      <c r="D518" s="31" t="n"/>
+      <c r="E518" s="31" t="n"/>
+      <c r="F518" s="31" t="n"/>
+    </row>
+    <row r="519" ht="24" customHeight="1">
+      <c r="A519" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B519" s="30" t="inlineStr">
+        <is>
+          <t>내 교재 문장이 배정돼 있으면 그 문장으로 나와요.</t>
+        </is>
+      </c>
+      <c r="C519" s="31" t="n"/>
+      <c r="D519" s="31" t="n"/>
+      <c r="E519" s="31" t="n"/>
+      <c r="F519" s="31" t="n"/>
+    </row>
+    <row r="520" ht="24" customHeight="1">
+      <c r="A520" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B520" s="30" t="inlineStr">
+        <is>
+          <t>제한 시간이 있어 속도감 있게 반복 연습돼요.</t>
+        </is>
+      </c>
+      <c r="C520" s="31" t="n"/>
+      <c r="D520" s="31" t="n"/>
+      <c r="E520" s="31" t="n"/>
+      <c r="F520" s="31" t="n"/>
+    </row>
+    <row r="521" ht="30" customHeight="1">
+      <c r="A521" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 소리 내어 따라 읽으면서 올리면 어순이 훨씬 빨리 몸에 붙어요.</t>
+        </is>
+      </c>
+      <c r="B521" s="33" t="n"/>
+      <c r="C521" s="33" t="n"/>
+      <c r="D521" s="33" t="n"/>
+      <c r="E521" s="33" t="n"/>
+      <c r="F521" s="33" t="n"/>
+    </row>
+    <row r="523" ht="26" customHeight="1">
+      <c r="A523" s="21" t="inlineStr">
+        <is>
+          <t>46  🧱 단어 테트리스  —  단어 조각을 쌓아 문장 두 줄 완성</t>
+        </is>
+      </c>
+      <c r="B523" s="22" t="n"/>
+      <c r="C523" s="22" t="n"/>
+      <c r="D523" s="22" t="n"/>
+      <c r="E523" s="22" t="n"/>
+      <c r="F523" s="22" t="n"/>
+    </row>
+    <row r="524" ht="42" customHeight="1">
+      <c r="A524" s="23" t="inlineStr">
+        <is>
+          <t>📖 정통 테트리스에 단어를 얹은 게임이에요. 단어가 문장 순서대로 하나씩 떨어지는데, 잘 쌓아서 줄을 채우면 문장이 완성돼요. 긴 단어는 넓은 조각, 짧은 단어는 작은 조각 — 끼워 맞추다 보면 단어가 저절로 외워져요.</t>
+        </is>
+      </c>
+      <c r="B524" s="24" t="n"/>
+      <c r="C524" s="24" t="n"/>
+      <c r="D524" s="24" t="n"/>
+      <c r="E524" s="24" t="n"/>
+      <c r="F524" s="24" t="n"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B525" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="526" ht="30" customHeight="1">
+      <c r="A526" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B526" s="28" t="inlineStr">
+        <is>
+          <t>학습 게임 허브에서 🧱 단어 테트리스를 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527" ht="30" customHeight="1">
+      <c r="A527" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B527" s="28" t="inlineStr">
+        <is>
+          <t>US 영어 모드 / CN 중국어 모드 중 하나를 골라요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528" ht="30" customHeight="1">
+      <c r="A528" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B528" s="28" t="inlineStr">
+        <is>
+          <t>◀ ▶ 이동 · 회전 · ▼ 빨리 · ↓ 한번에 떨어뜨리기로 조각을 놓아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529" ht="30" customHeight="1">
+      <c r="A529" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B529" s="28" t="inlineStr">
+        <is>
+          <t>조각을 놓을 때마다 발음이 들려요 — 듣고 따라 하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530" ht="24" customHeight="1">
+      <c r="A530" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B530" s="30" t="inlineStr">
+        <is>
+          <t>영어·중국어 두 모드를 같은 방식으로 즐길 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C530" s="31" t="n"/>
+      <c r="D530" s="31" t="n"/>
+      <c r="E530" s="31" t="n"/>
+      <c r="F530" s="31" t="n"/>
+    </row>
+    <row r="531" ht="24" customHeight="1">
+      <c r="A531" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B531" s="30" t="inlineStr">
+        <is>
+          <t>최고 기록이 저장돼서 다음에 다시 도전할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C531" s="31" t="n"/>
+      <c r="D531" s="31" t="n"/>
+      <c r="E531" s="31" t="n"/>
+      <c r="F531" s="31" t="n"/>
+    </row>
+    <row r="532" ht="24" customHeight="1">
+      <c r="A532" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B532" s="30" t="inlineStr">
+        <is>
+          <t>휴대폰에서도 화면이 잘리지 않게 정돈돼 있어요.</t>
+        </is>
+      </c>
+      <c r="C532" s="31" t="n"/>
+      <c r="D532" s="31" t="n"/>
+      <c r="E532" s="31" t="n"/>
+      <c r="F532" s="31" t="n"/>
+    </row>
+    <row r="533" ht="30" customHeight="1">
+      <c r="A533" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 긴 단어를 먼저 아래쪽에 깔아두면 줄을 훨씬 쉽게 채울 수 있어요.</t>
+        </is>
+      </c>
+      <c r="B533" s="33" t="n"/>
+      <c r="C533" s="33" t="n"/>
+      <c r="D533" s="33" t="n"/>
+      <c r="E533" s="33" t="n"/>
+      <c r="F533" s="33" t="n"/>
+    </row>
+    <row r="535" ht="26" customHeight="1">
+      <c r="A535" s="21" t="inlineStr">
+        <is>
+          <t>47  🛡️ 셔먼 탱크대전 · 랭귀지 에이스  —  어순대로 격파 · 조종하며 배우는 액션 학습</t>
+        </is>
+      </c>
+      <c r="B535" s="22" t="n"/>
+      <c r="C535" s="22" t="n"/>
+      <c r="D535" s="22" t="n"/>
+      <c r="E535" s="22" t="n"/>
+      <c r="F535" s="22" t="n"/>
+    </row>
+    <row r="536" ht="42" customHeight="1">
+      <c r="A536" s="23" t="inlineStr">
+        <is>
+          <t>📖 움직이며 배우는 액션형 학습 게임 두 가지가 새로 들어왔어요. 셔먼 탱크대전은 문장의 단어를 실은 적 전차를 어순대로 격파하는 게임이고, 랭귀지 에이스는 비행하며 문제를 맞히는 게임이에요. 손이 바쁜 만큼 집중이 잘 되고 반복이 지루하지 않아요.</t>
+        </is>
+      </c>
+      <c r="B536" s="24" t="n"/>
+      <c r="C536" s="24" t="n"/>
+      <c r="D536" s="24" t="n"/>
+      <c r="E536" s="24" t="n"/>
+      <c r="F536" s="24" t="n"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B537" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="538" ht="30" customHeight="1">
+      <c r="A538" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B538" s="28" t="inlineStr">
+        <is>
+          <t>학습 게임 허브에서 🛡️ 셔먼 탱크대전 또는 ✈️ 랭귀지 에이스를 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539" ht="30" customHeight="1">
+      <c r="A539" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B539" s="28" t="inlineStr">
+        <is>
+          <t>탱크대전은 English / 中文과 전장(초원·사막·설원), 난이도 1~7을 골라요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540" ht="30" customHeight="1">
+      <c r="A540" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B540" s="28" t="inlineStr">
+        <is>
+          <t>왼쪽 버튼을 누른 채 끌면 이동, 짧게 탭하면 그 방향으로 발사예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541" ht="30" customHeight="1">
+      <c r="A541" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B541" s="28" t="inlineStr">
+        <is>
+          <t>위 문장의 금색 단어를 실은 전차를 순서대로 격파해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542" ht="30" customHeight="1">
+      <c r="A542" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B542" s="28" t="inlineStr">
+        <is>
+          <t>젤리 연료통을 먹으면 시간이 늘어나요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543" ht="24" customHeight="1">
+      <c r="A543" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B543" s="30" t="inlineStr">
+        <is>
+          <t>난이도를 올리면 적이 빨라지고 발음도 빨라져요 — 듣기 훈련이 함께 돼요.</t>
+        </is>
+      </c>
+      <c r="C543" s="31" t="n"/>
+      <c r="D543" s="31" t="n"/>
+      <c r="E543" s="31" t="n"/>
+      <c r="F543" s="31" t="n"/>
+    </row>
+    <row r="544" ht="24" customHeight="1">
+      <c r="A544" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B544" s="30" t="inlineStr">
+        <is>
+          <t>교재 문장이 배정돼 있으면 그 문장으로 나와요.</t>
+        </is>
+      </c>
+      <c r="C544" s="31" t="n"/>
+      <c r="D544" s="31" t="n"/>
+      <c r="E544" s="31" t="n"/>
+      <c r="F544" s="31" t="n"/>
+    </row>
+    <row r="545" ht="24" customHeight="1">
+      <c r="A545" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B545" s="30" t="inlineStr">
+        <is>
+          <t>휴대폰·태블릿에서 손가락 조작만으로 다 됩니다.</t>
+        </is>
+      </c>
+      <c r="C545" s="31" t="n"/>
+      <c r="D545" s="31" t="n"/>
+      <c r="E545" s="31" t="n"/>
+      <c r="F545" s="31" t="n"/>
+    </row>
+    <row r="546" ht="26" customHeight="1">
+      <c r="A546" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 움직임이 많은 게임이에요. 저사양 기기에서 느리면 난이도를 낮춰 주세요.</t>
+        </is>
+      </c>
+      <c r="B546" s="35" t="n"/>
+      <c r="C546" s="35" t="n"/>
+      <c r="D546" s="35" t="n"/>
+      <c r="E546" s="35" t="n"/>
+      <c r="F546" s="35" t="n"/>
+    </row>
+    <row r="547" ht="30" customHeight="1">
+      <c r="A547" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 게임은 수업 뒤 복습용으로 쓸 때 효과가 가장 좋아요.</t>
+        </is>
+      </c>
+      <c r="B547" s="33" t="n"/>
+      <c r="C547" s="33" t="n"/>
+      <c r="D547" s="33" t="n"/>
+      <c r="E547" s="33" t="n"/>
+      <c r="F547" s="33" t="n"/>
+    </row>
+    <row r="549" ht="26" customHeight="1">
+      <c r="A549" s="21" t="inlineStr">
+        <is>
+          <t>48  🔐 얼굴 · 지문으로 로그인 (패스키)  —  앱에서 비밀번호 없이 한 번에</t>
+        </is>
+      </c>
+      <c r="B549" s="22" t="n"/>
+      <c r="C549" s="22" t="n"/>
+      <c r="D549" s="22" t="n"/>
+      <c r="E549" s="22" t="n"/>
+      <c r="F549" s="22" t="n"/>
+    </row>
+    <row r="550" ht="42" customHeight="1">
+      <c r="A550" s="23" t="inlineStr">
+        <is>
+          <t>📖 망고아이 앱(안드로이드) 에서 얼굴·지문으로 바로 로그인할 수 있게 됐어요. 한 번 등록해 두면 다음부터는 아이디·비밀번호를 칠 필요 없이 화면을 보거나 손가락만 대면 들어가져요. 비밀번호가 기기 밖으로 나가지 않아 더 안전해요.</t>
+        </is>
+      </c>
+      <c r="B550" s="24" t="n"/>
+      <c r="C550" s="24" t="n"/>
+      <c r="D550" s="24" t="n"/>
+      <c r="E550" s="24" t="n"/>
+      <c r="F550" s="24" t="n"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B551" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="552" ht="30" customHeight="1">
+      <c r="A552" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B552" s="28" t="inlineStr">
+        <is>
+          <t>앱을 최신 버전(v1.9 이상) 으로 올려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="553" ht="30" customHeight="1">
+      <c r="A553" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B553" s="28" t="inlineStr">
+        <is>
+          <t>평소처럼 아이디·비밀번호로 한 번 로그인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554" ht="30" customHeight="1">
+      <c r="A554" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B554" s="28" t="inlineStr">
+        <is>
+          <t>안내가 뜨면 패스키 등록을 눌러 얼굴·지문을 등록해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555" ht="30" customHeight="1">
+      <c r="A555" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B555" s="28" t="inlineStr">
+        <is>
+          <t>다음부터는 로그인 화면에서 얼굴·지문으로 바로 들어가요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556" ht="24" customHeight="1">
+      <c r="A556" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B556" s="30" t="inlineStr">
+        <is>
+          <t>비밀번호는 내 휴대폰 안에만 남고 서버로 가지 않아요.</t>
+        </is>
+      </c>
+      <c r="C556" s="31" t="n"/>
+      <c r="D556" s="31" t="n"/>
+      <c r="E556" s="31" t="n"/>
+      <c r="F556" s="31" t="n"/>
+    </row>
+    <row r="557" ht="24" customHeight="1">
+      <c r="A557" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B557" s="30" t="inlineStr">
+        <is>
+          <t>기기를 바꾸면 새 기기에서 다시 한 번 등록하면 돼요.</t>
+        </is>
+      </c>
+      <c r="C557" s="31" t="n"/>
+      <c r="D557" s="31" t="n"/>
+      <c r="E557" s="31" t="n"/>
+      <c r="F557" s="31" t="n"/>
+    </row>
+    <row r="558" ht="24" customHeight="1">
+      <c r="A558" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B558" s="30" t="inlineStr">
+        <is>
+          <t>패스키가 안 되는 기기는 기존 아이디·비밀번호 로그인이 그대로 됩니다.</t>
+        </is>
+      </c>
+      <c r="C558" s="31" t="n"/>
+      <c r="D558" s="31" t="n"/>
+      <c r="E558" s="31" t="n"/>
+      <c r="F558" s="31" t="n"/>
+    </row>
+    <row r="559" ht="26" customHeight="1">
+      <c r="A559" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 이 기능은 앱 전용이에요. 웹 브라우저에서는 기존 방식으로 로그인하세요.</t>
+        </is>
+      </c>
+      <c r="B559" s="35" t="n"/>
+      <c r="C559" s="35" t="n"/>
+      <c r="D559" s="35" t="n"/>
+      <c r="E559" s="35" t="n"/>
+      <c r="F559" s="35" t="n"/>
+    </row>
+    <row r="560" ht="30" customHeight="1">
+      <c r="A560" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 어린 학생일수록 비밀번호를 자주 잊어버려요. 패스키를 등록해 두면 문의가 크게 줄어요.</t>
+        </is>
+      </c>
+      <c r="B560" s="33" t="n"/>
+      <c r="C560" s="33" t="n"/>
+      <c r="D560" s="33" t="n"/>
+      <c r="E560" s="33" t="n"/>
+      <c r="F560" s="33" t="n"/>
+    </row>
+    <row r="562" ht="26" customHeight="1">
+      <c r="A562" s="21" t="inlineStr">
+        <is>
+          <t>49  🎤 말하기가 잘 안 끊겨요 · AI 친구도 똑똑해졌어요  —  천천히 말해도 기다려 줘요</t>
+        </is>
+      </c>
+      <c r="B562" s="22" t="n"/>
+      <c r="C562" s="22" t="n"/>
+      <c r="D562" s="22" t="n"/>
+      <c r="E562" s="22" t="n"/>
+      <c r="F562" s="22" t="n"/>
+    </row>
+    <row r="563" ht="42" customHeight="1">
+      <c r="A563" s="23" t="inlineStr">
+        <is>
+          <t>📖 천천히 말하거나 중간에 생각하느라 잠깐 멈추면 마이크가 먼저 꺼져 버리던 문제를 고쳤어요. 이제 상황에 따라 기다리는 시간이 달라지고, 휴대폰이 마이크를 제멋대로 끊어도 자동으로 다시 켜져요. AI 친구(Mango) 도 같은 말을 반복하지 않고, 말이 잘렸으면 되물어 주고, “천천히 말해 줘”라고 하면 실제로 천천히 말해 줘요.</t>
+        </is>
+      </c>
+      <c r="B563" s="24" t="n"/>
+      <c r="C563" s="24" t="n"/>
+      <c r="D563" s="24" t="n"/>
+      <c r="E563" s="24" t="n"/>
+      <c r="F563" s="24" t="n"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B564" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="565" ht="30" customHeight="1">
+      <c r="A565" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B565" s="28" t="inlineStr">
+        <is>
+          <t>말하기 코치·AI 웜업·AI 친구에서 🎤 버튼을 눌러 말해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566" ht="30" customHeight="1">
+      <c r="A566" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B566" s="28" t="inlineStr">
+        <is>
+          <t>생각하느라 잠깐 멈춰도 괜찮아요 — 끝났다고 판단할 때까지 기다려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567" ht="30" customHeight="1">
+      <c r="A567" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B567" s="28" t="inlineStr">
+        <is>
+          <t>AI 친구에게 “천천히 말해 줘” 라고 하면 속도를 낮춰서 말해 줘요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568" ht="30" customHeight="1">
+      <c r="A568" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B568" s="28" t="inlineStr">
+        <is>
+          <t>목소리는 남자 · 여자 · 번갈아 중에서 고를 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569" ht="24" customHeight="1">
+      <c r="A569" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B569" s="30" t="inlineStr">
+        <is>
+          <t>안드로이드 휴대폰에서 마이크가 갑자기 끊기던 현상이 자동 복구돼요.</t>
+        </is>
+      </c>
+      <c r="C569" s="31" t="n"/>
+      <c r="D569" s="31" t="n"/>
+      <c r="E569" s="31" t="n"/>
+      <c r="F569" s="31" t="n"/>
+    </row>
+    <row r="570" ht="24" customHeight="1">
+      <c r="A570" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B570" s="30" t="inlineStr">
+        <is>
+          <t>AI 친구가 같은 문장을 반복하지 않아요.</t>
+        </is>
+      </c>
+      <c r="C570" s="31" t="n"/>
+      <c r="D570" s="31" t="n"/>
+      <c r="E570" s="31" t="n"/>
+      <c r="F570" s="31" t="n"/>
+    </row>
+    <row r="571" ht="24" customHeight="1">
+      <c r="A571" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B571" s="30" t="inlineStr">
+        <is>
+          <t>말이 중간에 잘리면 AI가 “이렇게 말한 거 맞아요?” 하고 확인해 줘요.</t>
+        </is>
+      </c>
+      <c r="C571" s="31" t="n"/>
+      <c r="D571" s="31" t="n"/>
+      <c r="E571" s="31" t="n"/>
+      <c r="F571" s="31" t="n"/>
+    </row>
+    <row r="572" ht="26" customHeight="1">
+      <c r="A572" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 주변이 시끄러우면 인식이 어려워요. 조용한 곳에서 또박또박 말해 주세요.</t>
+        </is>
+      </c>
+      <c r="B572" s="35" t="n"/>
+      <c r="C572" s="35" t="n"/>
+      <c r="D572" s="35" t="n"/>
+      <c r="E572" s="35" t="n"/>
+      <c r="F572" s="35" t="n"/>
+    </row>
+    <row r="573" ht="30" customHeight="1">
+      <c r="A573" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 이어폰 마이크를 쓰면 인식률이 눈에 띄게 올라가요.</t>
+        </is>
+      </c>
+      <c r="B573" s="33" t="n"/>
+      <c r="C573" s="33" t="n"/>
+      <c r="D573" s="33" t="n"/>
+      <c r="E573" s="33" t="n"/>
+      <c r="F573" s="33" t="n"/>
+    </row>
+    <row r="575" ht="26" customHeight="1">
+      <c r="A575" s="21" t="inlineStr">
+        <is>
+          <t>50  💳 수강신청 · 결제 한 번에  —  강사·요일·시간 고르고 결제하면 수업이 자동으로</t>
+        </is>
+      </c>
+      <c r="B575" s="22" t="n"/>
+      <c r="C575" s="22" t="n"/>
+      <c r="D575" s="22" t="n"/>
+      <c r="E575" s="22" t="n"/>
+      <c r="F575" s="22" t="n"/>
+    </row>
+    <row r="576" ht="42" customHeight="1">
+      <c r="A576" s="23" t="inlineStr">
+        <is>
+          <t>📖 이제 강사와 요일·시간을 직접 고르고 결제하면, 수업 일정이 자동으로 전부 잡혀요. 결제 후에 따로 연락해서 시간표를 맞출 필요가 없어요. 이미 다른 수업이 있는 시간은 결제 전에 미리 알려 줘요.</t>
+        </is>
+      </c>
+      <c r="B576" s="24" t="n"/>
+      <c r="C576" s="24" t="n"/>
+      <c r="D576" s="24" t="n"/>
+      <c r="E576" s="24" t="n"/>
+      <c r="F576" s="24" t="n"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B577" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="578" ht="30" customHeight="1">
+      <c r="A578" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B578" s="28" t="inlineStr">
+        <is>
+          <t>수강신청 화면을 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579" ht="30" customHeight="1">
+      <c r="A579" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B579" s="28" t="inlineStr">
+        <is>
+          <t>① 강사 선택 — 원하는 선생님을 골라요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="580" ht="30" customHeight="1">
+      <c r="A580" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B580" s="28" t="inlineStr">
+        <is>
+          <t>② 수업 옵션 — 주 횟수(주1~5회) · 기간(1·3·6·12개월) · 수업 길이(20분/40분)를 골라요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581" ht="30" customHeight="1">
+      <c r="A581" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B581" s="28" t="inlineStr">
+        <is>
+          <t>③ 요일·시간 — 요일을 주 횟수만큼 고르고 시작 시각·시작일을 정해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582" ht="30" customHeight="1">
+      <c r="A582" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B582" s="28" t="inlineStr">
+        <is>
+          <t>✅ 예약 가능이 뜨면 아래 결제하기를 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="583" ht="30" customHeight="1">
+      <c r="A583" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B583" s="28" t="inlineStr">
+        <is>
+          <t>결제가 끝나면 전체 회차가 한꺼번에 생성돼요. 마이페이지에서 확인하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584" ht="24" customHeight="1">
+      <c r="A584" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B584" s="30" t="inlineStr">
+        <is>
+          <t>6개월 -5% · 12개월 -10% 처럼 기간이 길수록 할인돼요.</t>
+        </is>
+      </c>
+      <c r="C584" s="31" t="n"/>
+      <c r="D584" s="31" t="n"/>
+      <c r="E584" s="31" t="n"/>
+      <c r="F584" s="31" t="n"/>
+    </row>
+    <row r="585" ht="24" customHeight="1">
+      <c r="A585" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B585" s="30" t="inlineStr">
+        <is>
+          <t>고른 시간에 다른 수업이 있으면 ❌ 표시가 떠서 결제 전에 바꿀 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C585" s="31" t="n"/>
+      <c r="D585" s="31" t="n"/>
+      <c r="E585" s="31" t="n"/>
+      <c r="F585" s="31" t="n"/>
+    </row>
+    <row r="586" ht="24" customHeight="1">
+      <c r="A586" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B586" s="30" t="inlineStr">
+        <is>
+          <t>연기는 수업 30분 전까지 무료, 재결제 시 같은 요일·시간·강사로 자동 연장돼요.</t>
+        </is>
+      </c>
+      <c r="C586" s="31" t="n"/>
+      <c r="D586" s="31" t="n"/>
+      <c r="E586" s="31" t="n"/>
+      <c r="F586" s="31" t="n"/>
+    </row>
+    <row r="587" ht="26" customHeight="1">
+      <c r="A587" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 결제가 확인된 뒤에 수업이 생성돼요. 결제 직후 잠시 기다리면 일정이 나타납니다.</t>
+        </is>
+      </c>
+      <c r="B587" s="35" t="n"/>
+      <c r="C587" s="35" t="n"/>
+      <c r="D587" s="35" t="n"/>
+      <c r="E587" s="35" t="n"/>
+      <c r="F587" s="35" t="n"/>
+    </row>
+    <row r="588" ht="30" customHeight="1">
+      <c r="A588" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 학교 일정이 있는 요일은 피해서 고르세요. 나중에 바꾸는 것보다 처음에 잘 고르는 게 편해요.</t>
+        </is>
+      </c>
+      <c r="B588" s="33" t="n"/>
+      <c r="C588" s="33" t="n"/>
+      <c r="D588" s="33" t="n"/>
+      <c r="E588" s="33" t="n"/>
+      <c r="F588" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="450">
+  <mergeCells count="538">
     <mergeCell ref="A183:F183"/>
     <mergeCell ref="B209:F209"/>
     <mergeCell ref="B445:F445"/>
     <mergeCell ref="B301:F301"/>
     <mergeCell ref="B122:F122"/>
     <mergeCell ref="B432:F432"/>
+    <mergeCell ref="B537:F537"/>
     <mergeCell ref="B276:F276"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B512:F512"/>
     <mergeCell ref="B238:F238"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B278:F278"/>
+    <mergeCell ref="B551:F551"/>
+    <mergeCell ref="B538:F538"/>
+    <mergeCell ref="B532:F532"/>
+    <mergeCell ref="B578:F578"/>
     <mergeCell ref="A274:F274"/>
     <mergeCell ref="A372:F372"/>
+    <mergeCell ref="B515:F515"/>
     <mergeCell ref="A107:F107"/>
     <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A549:F549"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B133:F133"/>
+    <mergeCell ref="A536:F536"/>
     <mergeCell ref="B369:F369"/>
     <mergeCell ref="B418:F418"/>
     <mergeCell ref="A315:F315"/>
@@ -7902,12 +9178,14 @@
     <mergeCell ref="B160:F160"/>
     <mergeCell ref="A486:F486"/>
     <mergeCell ref="B489:F489"/>
+    <mergeCell ref="B527:F527"/>
     <mergeCell ref="B368:F368"/>
     <mergeCell ref="B135:F135"/>
     <mergeCell ref="B306:F306"/>
     <mergeCell ref="B433:F433"/>
     <mergeCell ref="A252:F252"/>
     <mergeCell ref="B227:F227"/>
+    <mergeCell ref="B531:F531"/>
     <mergeCell ref="B420:F420"/>
     <mergeCell ref="B199:F199"/>
     <mergeCell ref="B370:F370"/>
@@ -7915,6 +9193,7 @@
     <mergeCell ref="B291:F291"/>
     <mergeCell ref="A425:F425"/>
     <mergeCell ref="B228:F228"/>
+    <mergeCell ref="A562:F562"/>
     <mergeCell ref="A262:F262"/>
     <mergeCell ref="B88:F88"/>
     <mergeCell ref="B148:F148"/>
@@ -7927,9 +9206,11 @@
     <mergeCell ref="B317:F317"/>
     <mergeCell ref="B217:F217"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="B540:F540"/>
     <mergeCell ref="B319:F319"/>
     <mergeCell ref="B490:F490"/>
     <mergeCell ref="B383:F383"/>
+    <mergeCell ref="B554:F554"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A413:F413"/>
     <mergeCell ref="B439:F439"/>
@@ -7942,15 +9223,21 @@
     <mergeCell ref="B441:F441"/>
     <mergeCell ref="B161:F161"/>
     <mergeCell ref="B259:F259"/>
+    <mergeCell ref="B530:F530"/>
     <mergeCell ref="B136:F136"/>
+    <mergeCell ref="B505:F505"/>
+    <mergeCell ref="B499:F499"/>
     <mergeCell ref="B299:F299"/>
     <mergeCell ref="B225:F225"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B249:F249"/>
+    <mergeCell ref="A510:F510"/>
     <mergeCell ref="A295:F295"/>
     <mergeCell ref="A143:F143"/>
     <mergeCell ref="A334:F334"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A576:F576"/>
+    <mergeCell ref="A507:F507"/>
     <mergeCell ref="B91:F91"/>
     <mergeCell ref="B327:F327"/>
     <mergeCell ref="B454:F454"/>
@@ -7963,6 +9250,7 @@
     <mergeCell ref="B391:F391"/>
     <mergeCell ref="B247:F247"/>
     <mergeCell ref="B385:F385"/>
+    <mergeCell ref="B518:F518"/>
     <mergeCell ref="A302:F302"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="B151:F151"/>
@@ -7990,9 +9278,12 @@
     <mergeCell ref="B81:F81"/>
     <mergeCell ref="B366:F366"/>
     <mergeCell ref="B381:F381"/>
+    <mergeCell ref="B552:F552"/>
     <mergeCell ref="A386:F386"/>
+    <mergeCell ref="A508:F508"/>
     <mergeCell ref="B480:F480"/>
     <mergeCell ref="A373:F373"/>
+    <mergeCell ref="A573:F573"/>
     <mergeCell ref="B328:F328"/>
     <mergeCell ref="B455:F455"/>
     <mergeCell ref="A450:F450"/>
@@ -8001,13 +9292,17 @@
     <mergeCell ref="B172:F172"/>
     <mergeCell ref="B270:F270"/>
     <mergeCell ref="B392:F392"/>
+    <mergeCell ref="B568:F568"/>
     <mergeCell ref="B186:F186"/>
     <mergeCell ref="B457:F457"/>
     <mergeCell ref="B257:F257"/>
+    <mergeCell ref="B506:F506"/>
     <mergeCell ref="B288:F288"/>
+    <mergeCell ref="B555:F555"/>
     <mergeCell ref="B92:F92"/>
     <mergeCell ref="B394:F394"/>
     <mergeCell ref="A462:F462"/>
+    <mergeCell ref="B557:F557"/>
     <mergeCell ref="A399:F399"/>
     <mergeCell ref="A355:F355"/>
     <mergeCell ref="A305:F305"/>
@@ -8015,13 +9310,17 @@
     <mergeCell ref="A292:F292"/>
     <mergeCell ref="B125:F125"/>
     <mergeCell ref="B185:F185"/>
+    <mergeCell ref="B581:F581"/>
     <mergeCell ref="A223:F223"/>
     <mergeCell ref="B475:F475"/>
     <mergeCell ref="A294:F294"/>
     <mergeCell ref="B176:F176"/>
     <mergeCell ref="B347:F347"/>
     <mergeCell ref="B341:F341"/>
+    <mergeCell ref="B583:F583"/>
     <mergeCell ref="B468:F468"/>
+    <mergeCell ref="B539:F539"/>
+    <mergeCell ref="B577:F577"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="A254:F254"/>
     <mergeCell ref="B405:F405"/>
@@ -8042,6 +9341,7 @@
     <mergeCell ref="B75:F75"/>
     <mergeCell ref="B62:F62"/>
     <mergeCell ref="A282:F282"/>
+    <mergeCell ref="B571:F571"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A242:F242"/>
     <mergeCell ref="B39:F39"/>
@@ -8065,6 +9365,7 @@
     <mergeCell ref="A402:F402"/>
     <mergeCell ref="B428:F428"/>
     <mergeCell ref="B415:F415"/>
+    <mergeCell ref="B586:F586"/>
     <mergeCell ref="A168:F168"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B123:F123"/>
@@ -8072,10 +9373,13 @@
     <mergeCell ref="B110:F110"/>
     <mergeCell ref="B286:F286"/>
     <mergeCell ref="B479:F479"/>
+    <mergeCell ref="B584:F584"/>
+    <mergeCell ref="A547:F547"/>
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="A255:F255"/>
     <mergeCell ref="A364:F364"/>
     <mergeCell ref="A192:F192"/>
+    <mergeCell ref="B504:F504"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B248:F248"/>
@@ -8083,24 +9387,29 @@
     <mergeCell ref="B235:F235"/>
     <mergeCell ref="A96:F96"/>
     <mergeCell ref="B337:F337"/>
+    <mergeCell ref="B579:F579"/>
     <mergeCell ref="B103:F103"/>
     <mergeCell ref="B78:F78"/>
     <mergeCell ref="B205:F205"/>
     <mergeCell ref="B339:F339"/>
     <mergeCell ref="A352:F352"/>
+    <mergeCell ref="B501:F501"/>
     <mergeCell ref="A485:F485"/>
+    <mergeCell ref="B526:F526"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A410:F410"/>
     <mergeCell ref="B194:F194"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="A118:F118"/>
     <mergeCell ref="B492:F492"/>
+    <mergeCell ref="B528:F528"/>
     <mergeCell ref="A474:F474"/>
     <mergeCell ref="B131:F131"/>
     <mergeCell ref="B236:F236"/>
     <mergeCell ref="B307:F307"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B429:F429"/>
+    <mergeCell ref="B500:F500"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B465:F465"/>
     <mergeCell ref="B350:F350"/>
@@ -8109,11 +9418,14 @@
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="B287:F287"/>
     <mergeCell ref="B358:F358"/>
+    <mergeCell ref="B529:F529"/>
     <mergeCell ref="A200:F200"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="A265:F265"/>
+    <mergeCell ref="A563:F563"/>
     <mergeCell ref="B289:F289"/>
     <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A550:F550"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A202:F202"/>
     <mergeCell ref="B241:F241"/>
@@ -8128,16 +9440,19 @@
     <mergeCell ref="A447:F447"/>
     <mergeCell ref="A434:F434"/>
     <mergeCell ref="B219:F219"/>
+    <mergeCell ref="B517:F517"/>
     <mergeCell ref="A213:F213"/>
     <mergeCell ref="B210:F210"/>
     <mergeCell ref="A449:F449"/>
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="A424:F424"/>
+    <mergeCell ref="A495:F495"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B318:F318"/>
     <mergeCell ref="A482:F482"/>
     <mergeCell ref="A190:F190"/>
     <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B520:F520"/>
     <mergeCell ref="B308:F308"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B397:F397"/>
@@ -8149,31 +9464,43 @@
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B361:F361"/>
+    <mergeCell ref="A572:F572"/>
     <mergeCell ref="A493:F493"/>
     <mergeCell ref="B150:F150"/>
     <mergeCell ref="B321:F321"/>
     <mergeCell ref="B215:F215"/>
     <mergeCell ref="A139:F139"/>
     <mergeCell ref="A272:F272"/>
+    <mergeCell ref="B513:F513"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B152:F152"/>
     <mergeCell ref="A203:F203"/>
+    <mergeCell ref="B542:F542"/>
     <mergeCell ref="B229:F229"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B145:F145"/>
     <mergeCell ref="A140:F140"/>
+    <mergeCell ref="B514:F514"/>
     <mergeCell ref="B452:F452"/>
+    <mergeCell ref="B544:F544"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="B258:F258"/>
     <mergeCell ref="B147:F147"/>
     <mergeCell ref="B451:F451"/>
+    <mergeCell ref="B543:F543"/>
     <mergeCell ref="B481:F481"/>
     <mergeCell ref="B456:F456"/>
     <mergeCell ref="B260:F260"/>
+    <mergeCell ref="A521:F521"/>
+    <mergeCell ref="B545:F545"/>
+    <mergeCell ref="A496:F496"/>
     <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A523:F523"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B163:F163"/>
+    <mergeCell ref="A560:F560"/>
     <mergeCell ref="A354:F354"/>
+    <mergeCell ref="B570:F570"/>
     <mergeCell ref="B138:F138"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="B309:F309"/>
@@ -8198,12 +9525,17 @@
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="A275:F275"/>
     <mergeCell ref="B316:F316"/>
+    <mergeCell ref="B565:F565"/>
+    <mergeCell ref="A511:F511"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B266:F266"/>
     <mergeCell ref="B89:F89"/>
     <mergeCell ref="B393:F393"/>
     <mergeCell ref="B331:F331"/>
     <mergeCell ref="B453:F453"/>
+    <mergeCell ref="B502:F502"/>
+    <mergeCell ref="B558:F558"/>
+    <mergeCell ref="B564:F564"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B197:F197"/>
@@ -8211,13 +9543,18 @@
     <mergeCell ref="B268:F268"/>
     <mergeCell ref="B153:F153"/>
     <mergeCell ref="B395:F395"/>
+    <mergeCell ref="B566:F566"/>
+    <mergeCell ref="B553:F553"/>
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B261:F261"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="B184:F184"/>
+    <mergeCell ref="A587:F587"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A524:F524"/>
     <mergeCell ref="A97:F97"/>
     <mergeCell ref="A224:F224"/>
+    <mergeCell ref="A588:F588"/>
     <mergeCell ref="A72:F72"/>
     <mergeCell ref="B250:F250"/>
     <mergeCell ref="B166:F166"/>
@@ -8235,9 +9572,13 @@
     <mergeCell ref="B281:F281"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B256:F256"/>
+    <mergeCell ref="B497:F497"/>
+    <mergeCell ref="B541:F541"/>
+    <mergeCell ref="A535:F535"/>
     <mergeCell ref="A473:F473"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A575:F575"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="B121:F121"/>
@@ -8245,20 +9586,25 @@
     <mergeCell ref="A285:F285"/>
     <mergeCell ref="B357:F357"/>
     <mergeCell ref="B167:F167"/>
+    <mergeCell ref="B503:F503"/>
     <mergeCell ref="A85:F85"/>
     <mergeCell ref="B111:F111"/>
     <mergeCell ref="B421:F421"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B396:F396"/>
+    <mergeCell ref="B567:F567"/>
     <mergeCell ref="B175:F175"/>
     <mergeCell ref="B162:F162"/>
     <mergeCell ref="B267:F267"/>
     <mergeCell ref="B398:F398"/>
+    <mergeCell ref="B569:F569"/>
+    <mergeCell ref="B525:F525"/>
     <mergeCell ref="B269:F269"/>
     <mergeCell ref="A403:F403"/>
     <mergeCell ref="B187:F187"/>
     <mergeCell ref="A182:F182"/>
     <mergeCell ref="A304:F304"/>
+    <mergeCell ref="B556:F556"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="A461:F461"/>
     <mergeCell ref="B251:F251"/>
@@ -8267,21 +9613,25 @@
     <mergeCell ref="B216:F216"/>
     <mergeCell ref="B487:F487"/>
     <mergeCell ref="B414:F414"/>
+    <mergeCell ref="B585:F585"/>
     <mergeCell ref="B188:F188"/>
     <mergeCell ref="B109:F109"/>
     <mergeCell ref="B280:F280"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B218:F218"/>
     <mergeCell ref="B351:F351"/>
+    <mergeCell ref="B516:F516"/>
     <mergeCell ref="B416:F416"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B488:F488"/>
     <mergeCell ref="A179:F179"/>
     <mergeCell ref="B409:F409"/>
+    <mergeCell ref="B580:F580"/>
     <mergeCell ref="A322:F322"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B346:F346"/>
+    <mergeCell ref="B582:F582"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A324:F324"/>
     <mergeCell ref="A180:F180"/>
@@ -8296,12 +9646,14 @@
     <mergeCell ref="B164:F164"/>
     <mergeCell ref="B406:F406"/>
     <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B498:F498"/>
     <mergeCell ref="B206:F206"/>
     <mergeCell ref="A233:F233"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="B326:F326"/>
     <mergeCell ref="A104:F104"/>
     <mergeCell ref="B130:F130"/>
+    <mergeCell ref="A533:F533"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A312:F312"/>
     <mergeCell ref="A483:F483"/>
@@ -8321,8 +9673,11 @@
     <mergeCell ref="B427:F427"/>
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="B348:F348"/>
+    <mergeCell ref="B519:F519"/>
     <mergeCell ref="B419:F419"/>
     <mergeCell ref="B298:F298"/>
+    <mergeCell ref="A559:F559"/>
+    <mergeCell ref="A546:F546"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="A325:F325"/>
     <mergeCell ref="B51:F51"/>
